--- a/production/plantilla_prueba_100_uniones.xlsx
+++ b/production/plantilla_prueba_100_uniones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trsa-my.sharepoint.com/personal/aarbona_grupotr_es/Documents/Documentos/proyecto_uniones/production/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_5C81A1801653CF19AD81C9F0505ED87656CC60C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF110DF0-0826-4349-8548-2F1E366B501F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_5C81A1801653CF19AD81C9F0505ED87656CC60C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D282B01-F7B3-47BE-B379-C9A8B89F7CCB}"/>
   <bookViews>
-    <workbookView xWindow="-11820" yWindow="-13710" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12180" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_IA" sheetId="1" r:id="rId1"/>
@@ -461,13 +461,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -519,16 +525,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
         <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>333375</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:col>24</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>514350</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:col>29</xdr:col>
+          <xdr:colOff>542925</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>95250</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8060,16 +8066,16 @@
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>333375</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:col>24</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>57150</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>514350</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
+                    <xdr:col>29</xdr:col>
+                    <xdr:colOff>542925</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>95250</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
